--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.80362</v>
+        <v>17.16992</v>
       </c>
       <c r="D2" t="n">
-        <v>16.83901</v>
+        <v>16.69493</v>
       </c>
       <c r="E2" t="n">
-        <v>16.67222</v>
+        <v>16.85364</v>
       </c>
       <c r="F2" t="n">
-        <v>42.33161</v>
+        <v>42.59962</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05088</v>
+        <v>0.05084</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81768</v>
+        <v>1.86171</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.19846</v>
+        <v>17.22801</v>
       </c>
       <c r="D3" t="n">
-        <v>16.97804</v>
+        <v>16.54159</v>
       </c>
       <c r="E3" t="n">
-        <v>16.81365</v>
+        <v>16.69633</v>
       </c>
       <c r="F3" t="n">
-        <v>42.06031</v>
+        <v>42.81026</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05037</v>
+        <v>0.05064</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82278</v>
+        <v>1.84242</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.85102</v>
+        <v>17.00404</v>
       </c>
       <c r="D4" t="n">
-        <v>16.5843</v>
+        <v>16.76854</v>
       </c>
       <c r="E4" t="n">
-        <v>16.27059</v>
+        <v>16.89163</v>
       </c>
       <c r="F4" t="n">
-        <v>42.82113</v>
+        <v>41.89914</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0508</v>
+        <v>0.05055</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84685</v>
+        <v>1.80082</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89931</v>
+        <v>16.70239</v>
       </c>
       <c r="D6" t="n">
-        <v>16.26367</v>
+        <v>16.22295</v>
       </c>
       <c r="E6" t="n">
-        <v>16.58179</v>
+        <v>16.36908</v>
       </c>
       <c r="F6" t="n">
-        <v>22.49678</v>
+        <v>21.66975</v>
       </c>
       <c r="G6" t="n">
-        <v>34.01899</v>
+        <v>34.39255</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.6712</v>
+        <v>16.77099</v>
       </c>
       <c r="D7" t="n">
-        <v>16.2397</v>
+        <v>16.36962</v>
       </c>
       <c r="E7" t="n">
-        <v>16.3361</v>
+        <v>16.66203</v>
       </c>
       <c r="F7" t="n">
-        <v>21.65856</v>
+        <v>21.9087</v>
       </c>
       <c r="G7" t="n">
-        <v>34.27653</v>
+        <v>33.84854</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.8291</v>
+        <v>16.62314</v>
       </c>
       <c r="D8" t="n">
-        <v>16.18836</v>
+        <v>15.99996</v>
       </c>
       <c r="E8" t="n">
-        <v>16.3193</v>
+        <v>16.44497</v>
       </c>
       <c r="F8" t="n">
-        <v>21.83161</v>
+        <v>21.74161</v>
       </c>
       <c r="G8" t="n">
-        <v>34.68708</v>
+        <v>33.33006</v>
       </c>
     </row>
   </sheetData>
